--- a/Avantis Mapping/SPARQL_superclass.xlsx
+++ b/Avantis Mapping/SPARQL_superclass.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\medney\Documents\GitHub\TWONTO\Avantis Mapping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F16D84FD-BB73-48DA-B739-55D9128C163C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4F5A3B2-441B-405A-9B22-E2646F1CDB4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{716C0CF8-2E33-46F2-BE6F-578AC5702A19}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{716C0CF8-2E33-46F2-BE6F-578AC5702A19}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,42 +36,47 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>TWONTO</t>
   </si>
   <si>
+    <t>Meter</t>
+  </si>
+  <si>
     <t>Silencer</t>
   </si>
   <si>
     <t>Electrical Power Line</t>
   </si>
   <si>
+    <t>BUS bar greater than 750 volts_x000D_
+Control Panel,MCC_x000D_
+Motor Control Center_x000D_
+Motor Control Centre_x000D_
+Power Distribution Panel_x000D_
+Control Panel,MCC</t>
+  </si>
+  <si>
     <t>Pressure Indicator</t>
   </si>
   <si>
     <t>Super_Class</t>
   </si>
   <si>
-    <t>PREFIX rdf: &lt;http://www.w3.org/1999/02/22-rdf-syntax-ns#&gt;
-PREFIX owl: &lt;http://www.w3.org/2002/07/owl#&gt;
-PREFIX rdfs: &lt;http://www.w3.org/2000/01/rdf-schema#&gt;
-PREFIX xsd: &lt;http://www.w3.org/2001/XMLSchema#&gt;
-PREFIX tw: &lt;http://www.toronto.ca/TWONTO#&gt;
-SELECT (STR(?label) as ?TWONTO) (STR(?object) as ?Avantis)
-WHERE { 
-    ?entityIRI tw:is_superclass_of_avantis_class ?object ;
-              rdfs:label ?label .
-}</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#air_duct_segment</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#cable_segment</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#instrument_gauge_or_display</t>
+    <t>instrumentation</t>
+  </si>
+  <si>
+    <t>air_duct_segment</t>
+  </si>
+  <si>
+    <t>cable_segment</t>
+  </si>
+  <si>
+    <t>electrical_panel_or_cabinet</t>
+  </si>
+  <si>
+    <t>instrument_gauge_or_display</t>
   </si>
 </sst>
 </file>
@@ -184,8 +189,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D8A40142-39E5-42CA-9533-50AFBB2F55FD}" name="Table1" displayName="Table1" ref="A2:B5" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A2:B5" xr:uid="{D8A40142-39E5-42CA-9533-50AFBB2F55FD}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D8A40142-39E5-42CA-9533-50AFBB2F55FD}" name="Table1" displayName="Table1" ref="A2:B7" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A2:B7" xr:uid="{D8A40142-39E5-42CA-9533-50AFBB2F55FD}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{34BCA513-5439-4C7A-B816-5CB2BD0EC811}" name="TWONTO"/>
     <tableColumn id="2" xr3:uid="{FE07ACB4-50AE-40AB-B2F3-B5C5BACC68A9}" name="Super_Class"/>
@@ -491,48 +496,59 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C799550E-49B1-4512-9CC1-86876BA1337E}">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A2:B7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="56.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="61.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="56.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="61.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="165" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/Avantis Mapping/SPARQL_superclass.xlsx
+++ b/Avantis Mapping/SPARQL_superclass.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\medney\Documents\GitHub\TWONTO\Avantis Mapping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA73F88F-A1FD-4A30-A2EF-0848068E2761}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F16D84FD-BB73-48DA-B739-55D9128C163C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{716C0CF8-2E33-46F2-BE6F-578AC5702A19}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{716C0CF8-2E33-46F2-BE6F-578AC5702A19}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,72 +36,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>TWONTO</t>
   </si>
   <si>
+    <t>Silencer</t>
+  </si>
+  <si>
+    <t>Electrical Power Line</t>
+  </si>
+  <si>
     <t>Pressure Indicator</t>
   </si>
   <si>
     <t>Super_Class</t>
-  </si>
-  <si>
-    <t>Power Distribution Panel</t>
-  </si>
-  <si>
-    <t>Motor Control Centre</t>
-  </si>
-  <si>
-    <t>Motor Control Center</t>
-  </si>
-  <si>
-    <t>BUS bar greater than 750 volts</t>
-  </si>
-  <si>
-    <t>Switchgear</t>
-  </si>
-  <si>
-    <t>Control Panel,MCC</t>
-  </si>
-  <si>
-    <t>Electrical Power Line</t>
-  </si>
-  <si>
-    <t>Scissorlift</t>
-  </si>
-  <si>
-    <t>Silencer</t>
-  </si>
-  <si>
-    <t>Pneumatic System</t>
-  </si>
-  <si>
-    <t>Desktop</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#00110</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#00234</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#00111</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#00444</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#00144</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#00492</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#00445</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#00192</t>
   </si>
   <si>
     <t>PREFIX rdf: &lt;http://www.w3.org/1999/02/22-rdf-syntax-ns#&gt;
@@ -109,23 +58,20 @@
 PREFIX rdfs: &lt;http://www.w3.org/2000/01/rdf-schema#&gt;
 PREFIX xsd: &lt;http://www.w3.org/2001/XMLSchema#&gt;
 PREFIX tw: &lt;http://www.toronto.ca/TWONTO#&gt;
-SELECT (STR(?sub) AS ?TWONTO) (STR(?object) AS ?Avantis)
+SELECT (STR(?label) as ?TWONTO) (STR(?object) as ?Avantis)
 WHERE { 
-    ?sub tw:is_superclass_of_Avantis_class ?object .
-    FILTER NOT EXISTS { ?sub owl:deprecated "true"^^xsd:boolean }
+    ?entityIRI tw:is_superclass_of_avantis_class ?object ;
+              rdfs:label ?label .
 }</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#00408</t>
-  </si>
-  <si>
-    <t>IRG</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#00919</t>
-  </si>
-  <si>
-    <t>PLQ</t>
+    <t>http://www.toronto.ca/TWONTO#air_duct_segment</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#cable_segment</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#instrument_gauge_or_display</t>
   </si>
 </sst>
 </file>
@@ -149,15 +95,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color theme="10"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -170,6 +115,12 @@
         <bgColor rgb="FF4472C4"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E1F2"/>
+        <bgColor rgb="FFD9E1F2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -180,20 +131,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="1">
@@ -235,8 +184,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D8A40142-39E5-42CA-9533-50AFBB2F55FD}" name="Table1" displayName="Table1" ref="A2:B16" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A2:B16" xr:uid="{D8A40142-39E5-42CA-9533-50AFBB2F55FD}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D8A40142-39E5-42CA-9533-50AFBB2F55FD}" name="Table1" displayName="Table1" ref="A2:B5" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A2:B5" xr:uid="{D8A40142-39E5-42CA-9533-50AFBB2F55FD}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{34BCA513-5439-4C7A-B816-5CB2BD0EC811}" name="TWONTO"/>
     <tableColumn id="2" xr3:uid="{FE07ACB4-50AE-40AB-B2F3-B5C5BACC68A9}" name="Super_Class"/>
@@ -246,9 +195,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -286,7 +235,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -392,7 +341,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -534,7 +483,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -542,136 +491,48 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C799550E-49B1-4512-9CC1-86876BA1337E}">
-  <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="56.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="61.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="56.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="61.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="159.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
-        <v>22</v>
+    <row r="1" spans="1:2" ht="165" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
         <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16" t="s">
-        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/Avantis Mapping/SPARQL_superclass.xlsx
+++ b/Avantis Mapping/SPARQL_superclass.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\medney\Documents\GitHub\TWONTO\Avantis Mapping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4F5A3B2-441B-405A-9B22-E2646F1CDB4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F16D84FD-BB73-48DA-B739-55D9128C163C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{716C0CF8-2E33-46F2-BE6F-578AC5702A19}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{716C0CF8-2E33-46F2-BE6F-578AC5702A19}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,47 +36,42 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>TWONTO</t>
   </si>
   <si>
-    <t>Meter</t>
-  </si>
-  <si>
     <t>Silencer</t>
   </si>
   <si>
     <t>Electrical Power Line</t>
   </si>
   <si>
-    <t>BUS bar greater than 750 volts_x000D_
-Control Panel,MCC_x000D_
-Motor Control Center_x000D_
-Motor Control Centre_x000D_
-Power Distribution Panel_x000D_
-Control Panel,MCC</t>
-  </si>
-  <si>
     <t>Pressure Indicator</t>
   </si>
   <si>
     <t>Super_Class</t>
   </si>
   <si>
-    <t>instrumentation</t>
-  </si>
-  <si>
-    <t>air_duct_segment</t>
-  </si>
-  <si>
-    <t>cable_segment</t>
-  </si>
-  <si>
-    <t>electrical_panel_or_cabinet</t>
-  </si>
-  <si>
-    <t>instrument_gauge_or_display</t>
+    <t>PREFIX rdf: &lt;http://www.w3.org/1999/02/22-rdf-syntax-ns#&gt;
+PREFIX owl: &lt;http://www.w3.org/2002/07/owl#&gt;
+PREFIX rdfs: &lt;http://www.w3.org/2000/01/rdf-schema#&gt;
+PREFIX xsd: &lt;http://www.w3.org/2001/XMLSchema#&gt;
+PREFIX tw: &lt;http://www.toronto.ca/TWONTO#&gt;
+SELECT (STR(?label) as ?TWONTO) (STR(?object) as ?Avantis)
+WHERE { 
+    ?entityIRI tw:is_superclass_of_avantis_class ?object ;
+              rdfs:label ?label .
+}</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#air_duct_segment</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#cable_segment</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#instrument_gauge_or_display</t>
   </si>
 </sst>
 </file>
@@ -189,8 +184,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D8A40142-39E5-42CA-9533-50AFBB2F55FD}" name="Table1" displayName="Table1" ref="A2:B7" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A2:B7" xr:uid="{D8A40142-39E5-42CA-9533-50AFBB2F55FD}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D8A40142-39E5-42CA-9533-50AFBB2F55FD}" name="Table1" displayName="Table1" ref="A2:B5" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A2:B5" xr:uid="{D8A40142-39E5-42CA-9533-50AFBB2F55FD}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{34BCA513-5439-4C7A-B816-5CB2BD0EC811}" name="TWONTO"/>
     <tableColumn id="2" xr3:uid="{FE07ACB4-50AE-40AB-B2F3-B5C5BACC68A9}" name="Super_Class"/>
@@ -496,59 +491,48 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C799550E-49B1-4512-9CC1-86876BA1337E}">
-  <dimension ref="A2:B7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="56.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="61.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="56.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="61.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="165" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
-        <v>7</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" t="s">
-        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/Avantis Mapping/SPARQL_superclass.xlsx
+++ b/Avantis Mapping/SPARQL_superclass.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\medney\Documents\GitHub\TWONTO\Avantis Mapping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F16D84FD-BB73-48DA-B739-55D9128C163C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0700855F-D4DA-41F0-8CCD-1E26A3102E1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{716C0CF8-2E33-46F2-BE6F-578AC5702A19}"/>
   </bookViews>
@@ -36,15 +36,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
   <si>
     <t>TWONTO</t>
   </si>
   <si>
     <t>Silencer</t>
-  </si>
-  <si>
-    <t>Electrical Power Line</t>
   </si>
   <si>
     <t>Pressure Indicator</t>
@@ -68,10 +65,28 @@
     <t>http://www.toronto.ca/TWONTO#air_duct_segment</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#cable_segment</t>
-  </si>
-  <si>
     <t>http://www.toronto.ca/TWONTO#instrument_gauge_or_display</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#process_instrumentation</t>
+  </si>
+  <si>
+    <t>Meter</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#electrical_panel_or_cabinet</t>
+  </si>
+  <si>
+    <t>Power Distribution Panel</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#compactor</t>
+  </si>
+  <si>
+    <t>Transfer Compactor</t>
+  </si>
+  <si>
+    <t>Motor Control Centre</t>
   </si>
 </sst>
 </file>
@@ -184,8 +199,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D8A40142-39E5-42CA-9533-50AFBB2F55FD}" name="Table1" displayName="Table1" ref="A2:B5" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A2:B5" xr:uid="{D8A40142-39E5-42CA-9533-50AFBB2F55FD}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D8A40142-39E5-42CA-9533-50AFBB2F55FD}" name="Table1" displayName="Table1" ref="A2:B8" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A2:B8" xr:uid="{D8A40142-39E5-42CA-9533-50AFBB2F55FD}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{34BCA513-5439-4C7A-B816-5CB2BD0EC811}" name="TWONTO"/>
     <tableColumn id="2" xr3:uid="{FE07ACB4-50AE-40AB-B2F3-B5C5BACC68A9}" name="Super_Class"/>
@@ -195,9 +210,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -235,7 +250,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -341,7 +356,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -483,7 +498,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -491,7 +506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C799550E-49B1-4512-9CC1-86876BA1337E}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="56.7109375" bestFit="1" customWidth="1"/>
@@ -500,7 +515,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="165" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -508,31 +523,55 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/Avantis Mapping/SPARQL_superclass.xlsx
+++ b/Avantis Mapping/SPARQL_superclass.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\medney\Documents\GitHub\TWONTO\Avantis Mapping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0700855F-D4DA-41F0-8CCD-1E26A3102E1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EEF9E60-DD96-4935-92CD-084B55C82667}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{716C0CF8-2E33-46F2-BE6F-578AC5702A19}"/>
   </bookViews>
@@ -36,12 +36,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
   <si>
     <t>TWONTO</t>
-  </si>
-  <si>
-    <t>Silencer</t>
   </si>
   <si>
     <t>Pressure Indicator</t>
@@ -62,16 +59,7 @@
 }</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#air_duct_segment</t>
-  </si>
-  <si>
     <t>http://www.toronto.ca/TWONTO#instrument_gauge_or_display</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#process_instrumentation</t>
-  </si>
-  <si>
-    <t>Meter</t>
   </si>
   <si>
     <t>http://www.toronto.ca/TWONTO#electrical_panel_or_cabinet</t>
@@ -93,7 +81,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -109,15 +97,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -128,12 +109,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF4472C4"/>
         <bgColor rgb="FF4472C4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9E1F2"/>
-        <bgColor rgb="FFD9E1F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -149,10 +124,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -199,8 +173,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D8A40142-39E5-42CA-9533-50AFBB2F55FD}" name="Table1" displayName="Table1" ref="A2:B8" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A2:B8" xr:uid="{D8A40142-39E5-42CA-9533-50AFBB2F55FD}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D8A40142-39E5-42CA-9533-50AFBB2F55FD}" name="Table1" displayName="Table1" ref="A2:B6" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A2:B6" xr:uid="{D8A40142-39E5-42CA-9533-50AFBB2F55FD}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{34BCA513-5439-4C7A-B816-5CB2BD0EC811}" name="TWONTO"/>
     <tableColumn id="2" xr3:uid="{FE07ACB4-50AE-40AB-B2F3-B5C5BACC68A9}" name="Super_Class"/>
@@ -506,7 +480,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C799550E-49B1-4512-9CC1-86876BA1337E}">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="56.7109375" bestFit="1" customWidth="1"/>
@@ -514,8 +488,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="165" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>4</v>
+      <c r="A1" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -523,55 +497,39 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>8</v>
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Avantis Mapping/SPARQL_superclass.xlsx
+++ b/Avantis Mapping/SPARQL_superclass.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\medney\Documents\GitHub\TWONTO\Avantis Mapping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EEF9E60-DD96-4935-92CD-084B55C82667}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3539A519-DDE2-4B49-A769-2248AF79FAA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{716C0CF8-2E33-46F2-BE6F-578AC5702A19}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{716C0CF8-2E33-46F2-BE6F-578AC5702A19}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="16">
   <si>
     <t>TWONTO</t>
   </si>
@@ -75,6 +75,24 @@
   </si>
   <si>
     <t>Motor Control Centre</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#LV_electrical_panel</t>
+  </si>
+  <si>
+    <t>Motor Control Center</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#MV_electrical_cabinet</t>
+  </si>
+  <si>
+    <t>BUS bar greater than 750 volts</t>
+  </si>
+  <si>
+    <t>Switchgear</t>
+  </si>
+  <si>
+    <t>Control Panel,MCC</t>
   </si>
 </sst>
 </file>
@@ -173,8 +191,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D8A40142-39E5-42CA-9533-50AFBB2F55FD}" name="Table1" displayName="Table1" ref="A2:B6" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A2:B6" xr:uid="{D8A40142-39E5-42CA-9533-50AFBB2F55FD}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D8A40142-39E5-42CA-9533-50AFBB2F55FD}" name="Table1" displayName="Table1" ref="A2:B12" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A2:B12" xr:uid="{D8A40142-39E5-42CA-9533-50AFBB2F55FD}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{34BCA513-5439-4C7A-B816-5CB2BD0EC811}" name="TWONTO"/>
     <tableColumn id="2" xr3:uid="{FE07ACB4-50AE-40AB-B2F3-B5C5BACC68A9}" name="Super_Class"/>
@@ -480,19 +498,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C799550E-49B1-4512-9CC1-86876BA1337E}">
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="56.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="61.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="56.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="61.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="165" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -500,36 +518,84 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>5</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Avantis Mapping/SPARQL_superclass.xlsx
+++ b/Avantis Mapping/SPARQL_superclass.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\medney\Documents\GitHub\TWONTO\Avantis Mapping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3539A519-DDE2-4B49-A769-2248AF79FAA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E804EF86-CC89-49A5-8304-905A89A0474E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{716C0CF8-2E33-46F2-BE6F-578AC5702A19}"/>
+    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="10360" xr2:uid="{716C0CF8-2E33-46F2-BE6F-578AC5702A19}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -47,52 +47,52 @@
     <t>Super_Class</t>
   </si>
   <si>
+    <t>http://www.toronto.ca/TWONTO#instrument_gauge_or_display</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#electrical_panel_or_cabinet</t>
+  </si>
+  <si>
+    <t>Power Distribution Panel</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#compactor</t>
+  </si>
+  <si>
+    <t>Transfer Compactor</t>
+  </si>
+  <si>
+    <t>Motor Control Centre</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#LV_electrical_panel</t>
+  </si>
+  <si>
+    <t>Motor Control Center</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#MV_electrical_cabinet</t>
+  </si>
+  <si>
+    <t>BUS bar greater than 750 volts</t>
+  </si>
+  <si>
+    <t>Switchgear</t>
+  </si>
+  <si>
+    <t>Control Panel,MCC</t>
+  </si>
+  <si>
     <t>PREFIX rdf: &lt;http://www.w3.org/1999/02/22-rdf-syntax-ns#&gt;
 PREFIX owl: &lt;http://www.w3.org/2002/07/owl#&gt;
 PREFIX rdfs: &lt;http://www.w3.org/2000/01/rdf-schema#&gt;
 PREFIX xsd: &lt;http://www.w3.org/2001/XMLSchema#&gt;
 PREFIX tw: &lt;http://www.toronto.ca/TWONTO#&gt;
-SELECT (STR(?label) as ?TWONTO) (STR(?object) as ?Avantis)
+SELECT ?TWONTO (STR(?object) as ?Avantis)
 WHERE { 
-    ?entityIRI tw:is_superclass_of_avantis_class ?object ;
-              rdfs:label ?label .
+    ?TWONTO tw:is_superclass_of_avantis_class ?object .
+    FILTER NOT EXISTS { ?TWONTO owl:deprecated "true"^^xsd:boolean }
 }</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#instrument_gauge_or_display</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#electrical_panel_or_cabinet</t>
-  </si>
-  <si>
-    <t>Power Distribution Panel</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#compactor</t>
-  </si>
-  <si>
-    <t>Transfer Compactor</t>
-  </si>
-  <si>
-    <t>Motor Control Centre</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#LV_electrical_panel</t>
-  </si>
-  <si>
-    <t>Motor Control Center</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#MV_electrical_cabinet</t>
-  </si>
-  <si>
-    <t>BUS bar greater than 750 volts</t>
-  </si>
-  <si>
-    <t>Switchgear</t>
-  </si>
-  <si>
-    <t>Control Panel,MCC</t>
   </si>
 </sst>
 </file>
@@ -505,9 +505,9 @@
     <col min="2" max="2" width="61.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="174" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
@@ -520,71 +520,71 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
         <v>10</v>
-      </c>
-      <c r="B3" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
         <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
         <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B11" t="s">
         <v>1</v>
@@ -592,10 +592,10 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" t="s">
         <v>5</v>
-      </c>
-      <c r="B12" t="s">
-        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/Avantis Mapping/SPARQL_superclass.xlsx
+++ b/Avantis Mapping/SPARQL_superclass.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\medney\Documents\GitHub\TWONTO\Avantis Mapping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E804EF86-CC89-49A5-8304-905A89A0474E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F798449-7404-49A2-9410-3635DE484E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="10360" xr2:uid="{716C0CF8-2E33-46F2-BE6F-578AC5702A19}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{716C0CF8-2E33-46F2-BE6F-578AC5702A19}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
   <si>
     <t>TWONTO</t>
   </si>
@@ -47,31 +47,13 @@
     <t>Super_Class</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#instrument_gauge_or_display</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#electrical_panel_or_cabinet</t>
-  </si>
-  <si>
     <t>Power Distribution Panel</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#compactor</t>
-  </si>
-  <si>
-    <t>Transfer Compactor</t>
-  </si>
-  <si>
     <t>Motor Control Centre</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#LV_electrical_panel</t>
-  </si>
-  <si>
     <t>Motor Control Center</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#MV_electrical_cabinet</t>
   </si>
   <si>
     <t>BUS bar greater than 750 volts</t>
@@ -88,11 +70,51 @@
 PREFIX rdfs: &lt;http://www.w3.org/2000/01/rdf-schema#&gt;
 PREFIX xsd: &lt;http://www.w3.org/2001/XMLSchema#&gt;
 PREFIX tw: &lt;http://www.toronto.ca/TWONTO#&gt;
-SELECT ?TWONTO (STR(?object) as ?Avantis)
+SELECT (STR(?TWONTO_Label) AS ?Label) (STR(?object) AS ?Avantis)
 WHERE { 
-    ?TWONTO tw:is_superclass_of_avantis_class ?object .
+    ?TWONTO tw:is_superclass_of_Avantis_class ?object .
+    ?TWONTO rdfs:label ?TWONTO_Label .
     FILTER NOT EXISTS { ?TWONTO owl:deprecated "true"^^xsd:boolean }
 }</t>
+  </si>
+  <si>
+    <t>cable segment</t>
+  </si>
+  <si>
+    <t>Electrical Power Line</t>
+  </si>
+  <si>
+    <t>LV electrical panel</t>
+  </si>
+  <si>
+    <t>instrument gauge or display</t>
+  </si>
+  <si>
+    <t>man lift</t>
+  </si>
+  <si>
+    <t>Scissorlift</t>
+  </si>
+  <si>
+    <t>MV electrical cabinet</t>
+  </si>
+  <si>
+    <t>air duct segment</t>
+  </si>
+  <si>
+    <t>Silencer</t>
+  </si>
+  <si>
+    <t>instrument air or pneumatic system component</t>
+  </si>
+  <si>
+    <t>Pneumatic System</t>
+  </si>
+  <si>
+    <t>computer</t>
+  </si>
+  <si>
+    <t>Desktop</t>
   </si>
 </sst>
 </file>
@@ -191,8 +213,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D8A40142-39E5-42CA-9533-50AFBB2F55FD}" name="Table1" displayName="Table1" ref="A2:B12" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A2:B12" xr:uid="{D8A40142-39E5-42CA-9533-50AFBB2F55FD}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D8A40142-39E5-42CA-9533-50AFBB2F55FD}" name="Table1" displayName="Table1" ref="A2:B14" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A2:B14" xr:uid="{D8A40142-39E5-42CA-9533-50AFBB2F55FD}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{34BCA513-5439-4C7A-B816-5CB2BD0EC811}" name="TWONTO"/>
     <tableColumn id="2" xr3:uid="{FE07ACB4-50AE-40AB-B2F3-B5C5BACC68A9}" name="Super_Class"/>
@@ -498,16 +520,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C799550E-49B1-4512-9CC1-86876BA1337E}">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="56.7265625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="61.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="174" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="203" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
@@ -520,81 +542,97 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="B12" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
         <v>5</v>
       </c>
     </row>

--- a/Avantis Mapping/SPARQL_superclass.xlsx
+++ b/Avantis Mapping/SPARQL_superclass.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\medney\Documents\GitHub\TWONTO\Avantis Mapping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F798449-7404-49A2-9410-3635DE484E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E97205E-BF9C-4129-A733-CBF5804D8932}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{716C0CF8-2E33-46F2-BE6F-578AC5702A19}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{716C0CF8-2E33-46F2-BE6F-578AC5702A19}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -65,63 +65,62 @@
     <t>Control Panel,MCC</t>
   </si>
   <si>
+    <t>Electrical Power Line</t>
+  </si>
+  <si>
+    <t>Scissorlift</t>
+  </si>
+  <si>
+    <t>Silencer</t>
+  </si>
+  <si>
+    <t>Pneumatic System</t>
+  </si>
+  <si>
+    <t>Desktop</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00110</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00234</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00111</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00444</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00144</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00492</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00445</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00192</t>
+  </si>
+  <si>
     <t>PREFIX rdf: &lt;http://www.w3.org/1999/02/22-rdf-syntax-ns#&gt;
 PREFIX owl: &lt;http://www.w3.org/2002/07/owl#&gt;
 PREFIX rdfs: &lt;http://www.w3.org/2000/01/rdf-schema#&gt;
 PREFIX xsd: &lt;http://www.w3.org/2001/XMLSchema#&gt;
 PREFIX tw: &lt;http://www.toronto.ca/TWONTO#&gt;
-SELECT (STR(?TWONTO_Label) AS ?Label) (STR(?object) AS ?Avantis)
+SELECT (STR(?sub) AS ?TWONTO) (STR(?object) AS ?Avantis)
 WHERE { 
-    ?TWONTO tw:is_superclass_of_Avantis_class ?object .
-    ?TWONTO rdfs:label ?TWONTO_Label .
-    FILTER NOT EXISTS { ?TWONTO owl:deprecated "true"^^xsd:boolean }
+    ?sub tw:is_superclass_of_Avantis_class ?object .
+    FILTER NOT EXISTS { ?sub owl:deprecated "true"^^xsd:boolean }
 }</t>
-  </si>
-  <si>
-    <t>cable segment</t>
-  </si>
-  <si>
-    <t>Electrical Power Line</t>
-  </si>
-  <si>
-    <t>LV electrical panel</t>
-  </si>
-  <si>
-    <t>instrument gauge or display</t>
-  </si>
-  <si>
-    <t>man lift</t>
-  </si>
-  <si>
-    <t>Scissorlift</t>
-  </si>
-  <si>
-    <t>MV electrical cabinet</t>
-  </si>
-  <si>
-    <t>air duct segment</t>
-  </si>
-  <si>
-    <t>Silencer</t>
-  </si>
-  <si>
-    <t>instrument air or pneumatic system component</t>
-  </si>
-  <si>
-    <t>Pneumatic System</t>
-  </si>
-  <si>
-    <t>computer</t>
-  </si>
-  <si>
-    <t>Desktop</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -133,6 +132,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -161,17 +168,20 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="1">
@@ -527,9 +537,9 @@
     <col min="2" max="2" width="61.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="203" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
@@ -541,105 +551,108 @@
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>10</v>
+      <c r="A3" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A3" r:id="rId1" location="00110" xr:uid="{26164CB3-8D40-4445-8C36-9C3D34F6D757}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
--- a/Avantis Mapping/SPARQL_superclass.xlsx
+++ b/Avantis Mapping/SPARQL_superclass.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\medney\Documents\GitHub\TWONTO\Avantis Mapping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E97205E-BF9C-4129-A733-CBF5804D8932}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA73F88F-A1FD-4A30-A2EF-0848068E2761}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{716C0CF8-2E33-46F2-BE6F-578AC5702A19}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="27">
   <si>
     <t>TWONTO</t>
   </si>
@@ -114,6 +114,18 @@
     ?sub tw:is_superclass_of_Avantis_class ?object .
     FILTER NOT EXISTS { ?sub owl:deprecated "true"^^xsd:boolean }
 }</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00408</t>
+  </si>
+  <si>
+    <t>IRG</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00919</t>
+  </si>
+  <si>
+    <t>PLQ</t>
   </si>
 </sst>
 </file>
@@ -223,8 +235,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D8A40142-39E5-42CA-9533-50AFBB2F55FD}" name="Table1" displayName="Table1" ref="A2:B14" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A2:B14" xr:uid="{D8A40142-39E5-42CA-9533-50AFBB2F55FD}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D8A40142-39E5-42CA-9533-50AFBB2F55FD}" name="Table1" displayName="Table1" ref="A2:B16" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A2:B16" xr:uid="{D8A40142-39E5-42CA-9533-50AFBB2F55FD}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{34BCA513-5439-4C7A-B816-5CB2BD0EC811}" name="TWONTO"/>
     <tableColumn id="2" xr3:uid="{FE07ACB4-50AE-40AB-B2F3-B5C5BACC68A9}" name="Super_Class"/>
@@ -530,7 +542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C799550E-49B1-4512-9CC1-86876BA1337E}">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="56.7265625" bestFit="1" customWidth="1"/>
@@ -560,99 +572,112 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B12" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B13" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
         <v>21</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B16" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A3" r:id="rId1" location="00110" xr:uid="{26164CB3-8D40-4445-8C36-9C3D34F6D757}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>